--- a/docs/sprint-0/UserStoryDeliverable.xlsx
+++ b/docs/sprint-0/UserStoryDeliverable.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\files\documents\Class\Software Engineering\finapp\docs\sprint-0\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9EBC94-B607-45FB-937F-CE42EB8388FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="135" windowWidth="27960" windowHeight="12585"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +54,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -65,7 +71,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -102,30 +108,55 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -138,10 +169,56 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -150,13 +227,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -164,26 +239,236 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7DADFF54-A0E1-4F1B-9071-9023B1C1416B}" name="Table1" displayName="Table1" ref="A1:I31" insertRowShift="1" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="11" tableBorderDxfId="12">
+  <autoFilter ref="A1:I31" xr:uid="{7DADFF54-A0E1-4F1B-9071-9023B1C1416B}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{F1E08ECF-08BD-4D23-B99B-08B23B44915C}" name="ID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{7F7902A9-8E4C-46A3-8239-AF630DB06571}" name="Theme" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E547F1E7-75C6-4780-B883-D6F2E872CDC1}" name="As a/an" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{45F8AB4E-87E2-42F7-8602-63BFE211205F}" name="I want to…" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{CF371B4B-4074-45FF-BA55-E28199849CEB}" name="so that…" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{3B19EBBC-75FF-4708-8431-CD04347DBC75}" name="Notes" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F9038030-4142-44D3-A64C-F5E0A875000C}" name="Acceptance Critera / Conditions of Satisfaction" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{45310A0A-21DA-4FF4-9641-FD1EBBF58309}" name="Priority" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{5422640E-038B-45EA-A127-A92D30656783}" name="Status" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -221,7 +506,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -293,7 +578,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -466,45 +751,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="23.875" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -512,268 +800,348 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="13"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="13"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="13"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="13"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="13"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
